--- a/www/ig/fhir/sdo/StructureDefinition-esms-document-reference.xlsx
+++ b/www/ig/fhir/sdo/StructureDefinition-esms-document-reference.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T14:22:03+00:00</t>
+    <t>2026-06-29T08:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -659,7 +659,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -756,7 +756,7 @@
     <t>DocumentReference.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -992,7 +992,7 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.class</t>
@@ -1010,7 +1010,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1076,7 +1076,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1110,7 +1110,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1299,7 +1299,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1585,7 +1585,7 @@
     <t>Document Format Codes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.meta.profile</t>
@@ -1624,7 +1624,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1710,7 +1710,7 @@
     <t>XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -1743,7 +1743,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -1752,7 +1752,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1768,7 +1768,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2093,17 +2093,17 @@
   <dimension ref="A1:AQ78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.99609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2112,29 +2112,29 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="84.7890625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.0703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.69140625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="52.0078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="44.5859375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="84.2265625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="162.44921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="72.20703125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="139.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
